--- a/数据表/Datas/SpriteConfig_图片资源.xlsx
+++ b/数据表/Datas/SpriteConfig_图片资源.xlsx
@@ -108,6 +108,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">Sprite </t>
     </r>
     <r>
@@ -140,6 +146,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -459,6 +470,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -715,6 +731,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -1702,6 +1723,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -2091,6 +2117,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>
@@ -2320,6 +2351,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>##</t>
     </r>
     <r>

--- a/数据表/Datas/SpriteConfig_图片资源.xlsx
+++ b/数据表/Datas/SpriteConfig_图片资源.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="133">
   <si>
     <t>##var</t>
   </si>
@@ -108,36 +108,30 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">Sprite </t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">Sprite </t>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>索引（</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>索引（</t>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">-1 </t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">-1 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
@@ -148,14 +142,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
@@ -163,9 +149,6 @@
     </r>
   </si>
   <si>
-    <t>==========</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="12"/>
@@ -472,14 +455,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
@@ -733,14 +708,6 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
         <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
@@ -757,7 +724,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>常规</t>
@@ -1725,15 +1692,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>道具</t>
@@ -1741,6 +1701,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
@@ -1749,7 +1710,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>武器</t>
@@ -2119,15 +2081,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>道具</t>
@@ -2135,6 +2090,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
@@ -2143,7 +2099,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>防具</t>
@@ -2353,15 +2310,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>##</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>道具</t>
@@ -2369,6 +2319,7 @@
     <r>
       <rPr>
         <sz val="12"/>
+        <color rgb="FF202020"/>
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
@@ -2377,7 +2328,8 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>消耗品</t>
@@ -2395,16 +2347,44 @@
     </r>
   </si>
   <si>
-    <t>中小药</t>
-  </si>
-  <si>
-    <t>中药</t>
-  </si>
-  <si>
-    <t>中大药</t>
-  </si>
-  <si>
-    <t>大药</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中小药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中大药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大药</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2417,7 +2397,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2456,11 +2436,6 @@
       <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2628,7 +2603,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2964,153 +2939,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -3148,12 +3123,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -3694,18 +3663,18 @@
     </row>
     <row r="5" customHeight="1" spans="1:4">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:4">
       <c r="B6" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="2">
         <v>0</v>
@@ -3713,10 +3682,10 @@
     </row>
     <row r="7" customHeight="1" spans="1:4">
       <c r="B7" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D7" s="2">
         <v>1</v>
@@ -3724,10 +3693,10 @@
     </row>
     <row r="8" customHeight="1" spans="1:4">
       <c r="B8" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2">
         <v>2</v>
@@ -3735,10 +3704,10 @@
     </row>
     <row r="9" customHeight="1" spans="1:4">
       <c r="B9" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -3746,10 +3715,10 @@
     </row>
     <row r="10" customHeight="1" spans="1:4">
       <c r="B10" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
         <v>4</v>
@@ -3757,10 +3726,10 @@
     </row>
     <row r="11" customHeight="1" spans="1:4">
       <c r="B11" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11" s="2">
         <v>5</v>
@@ -3768,10 +3737,10 @@
     </row>
     <row r="12" customHeight="1" spans="1:4">
       <c r="B12" s="15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
         <v>6</v>
@@ -3779,10 +3748,10 @@
     </row>
     <row r="13" customHeight="1" spans="1:4">
       <c r="B13" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D13" s="2">
         <v>7</v>
@@ -3790,10 +3759,10 @@
     </row>
     <row r="14" customHeight="1" spans="1:4">
       <c r="B14" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14" s="2">
         <v>8</v>
@@ -3801,10 +3770,10 @@
     </row>
     <row r="15" customHeight="1" spans="1:4">
       <c r="B15" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
         <v>9</v>
@@ -3812,10 +3781,10 @@
     </row>
     <row r="16" customHeight="1" spans="1:4">
       <c r="B16" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D16" s="2">
         <v>10</v>
@@ -3823,10 +3792,10 @@
     </row>
     <row r="17" customHeight="1" spans="1:4">
       <c r="B17" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="2">
         <v>11</v>
@@ -3834,10 +3803,10 @@
     </row>
     <row r="18" customHeight="1" spans="1:4">
       <c r="B18" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2">
         <v>12</v>
@@ -3845,10 +3814,10 @@
     </row>
     <row r="19" customHeight="1" spans="1:4">
       <c r="B19" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2">
         <v>13</v>
@@ -3856,10 +3825,10 @@
     </row>
     <row r="20" customHeight="1" spans="1:4">
       <c r="B20" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D20" s="2">
         <v>14</v>
@@ -3870,18 +3839,18 @@
     </row>
     <row r="22" customHeight="1" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:4">
       <c r="B23" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="D23" s="2">
         <v>0</v>
@@ -3889,10 +3858,10 @@
     </row>
     <row r="24" customHeight="1" spans="1:4">
       <c r="B24" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
@@ -3900,10 +3869,10 @@
     </row>
     <row r="25" customHeight="1" spans="1:4">
       <c r="B25" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
@@ -3911,10 +3880,10 @@
     </row>
     <row r="26" customHeight="1" spans="1:4">
       <c r="B26" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
@@ -3922,10 +3891,10 @@
     </row>
     <row r="27" customHeight="1" spans="1:4">
       <c r="B27" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
@@ -3933,10 +3902,10 @@
     </row>
     <row r="28" customHeight="1" spans="1:4">
       <c r="B28" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28" s="2">
         <v>5</v>
@@ -3944,10 +3913,10 @@
     </row>
     <row r="29" customHeight="1" spans="1:4">
       <c r="B29" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
@@ -3955,10 +3924,10 @@
     </row>
     <row r="30" customHeight="1" spans="1:4">
       <c r="B30" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D30" s="2">
         <v>7</v>
@@ -3966,10 +3935,10 @@
     </row>
     <row r="31" customHeight="1" spans="1:4">
       <c r="B31" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D31" s="2">
         <v>8</v>
@@ -3977,10 +3946,10 @@
     </row>
     <row r="32" customHeight="1" spans="1:4">
       <c r="B32" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D32" s="2">
         <v>9</v>
@@ -3988,10 +3957,10 @@
     </row>
     <row r="33" customHeight="1" spans="1:4">
       <c r="B33" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D33" s="2">
         <v>10</v>
@@ -3999,10 +3968,10 @@
     </row>
     <row r="34" customHeight="1" spans="1:4">
       <c r="B34" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D34" s="2">
         <v>11</v>
@@ -4013,18 +3982,18 @@
     </row>
     <row r="37" customHeight="1" spans="1:4">
       <c r="A37" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="38" customHeight="1" spans="1:4">
       <c r="B38" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D38" s="2">
         <v>128</v>
@@ -4032,10 +4001,10 @@
     </row>
     <row r="39" customHeight="1" spans="1:4">
       <c r="B39" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D39" s="2">
         <v>129</v>
@@ -4043,10 +4012,10 @@
     </row>
     <row r="40" customHeight="1" spans="1:4">
       <c r="B40" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D40" s="2">
         <v>130</v>
@@ -4054,10 +4023,10 @@
     </row>
     <row r="41" customHeight="1" spans="1:4">
       <c r="B41" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41" s="2">
         <v>131</v>
@@ -4065,10 +4034,10 @@
     </row>
     <row r="42" customHeight="1" spans="1:4">
       <c r="B42" s="15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" s="2">
         <v>132</v>
@@ -4079,10 +4048,10 @@
     </row>
     <row r="44" customHeight="1" spans="1:4">
       <c r="B44" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D44" s="2">
         <v>224</v>
@@ -4090,10 +4059,10 @@
     </row>
     <row r="45" customHeight="1" spans="1:4">
       <c r="B45" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D45" s="2">
         <v>225</v>
@@ -4101,10 +4070,10 @@
     </row>
     <row r="46" customHeight="1" spans="1:4">
       <c r="B46" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D46" s="2">
         <v>226</v>
@@ -4112,10 +4081,10 @@
     </row>
     <row r="47" customHeight="1" spans="1:4">
       <c r="B47" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D47" s="2">
         <v>227</v>
@@ -4123,10 +4092,10 @@
     </row>
     <row r="48" customHeight="1" spans="1:4">
       <c r="B48" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D48" s="2">
         <v>228</v>
@@ -4134,10 +4103,10 @@
     </row>
     <row r="49" customHeight="1" spans="2:4">
       <c r="B49" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D49" s="2">
         <v>229</v>
@@ -4145,10 +4114,10 @@
     </row>
     <row r="50" customHeight="1" spans="2:4">
       <c r="B50" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D50" s="2">
         <v>230</v>
@@ -4156,10 +4125,10 @@
     </row>
     <row r="51" customHeight="1" spans="2:4">
       <c r="B51" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D51" s="2">
         <v>231</v>
@@ -4167,10 +4136,10 @@
     </row>
     <row r="52" customHeight="1" spans="2:4">
       <c r="B52" s="15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D52" s="2">
         <v>232</v>
@@ -4181,10 +4150,10 @@
     </row>
     <row r="54" customHeight="1" spans="2:4">
       <c r="B54" s="15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D54" s="2">
         <v>320</v>
@@ -4192,10 +4161,10 @@
     </row>
     <row r="55" customHeight="1" spans="2:4">
       <c r="B55" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D55" s="2">
         <v>321</v>
@@ -4203,10 +4172,10 @@
     </row>
     <row r="56" customHeight="1" spans="2:4">
       <c r="B56" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D56" s="2">
         <v>322</v>
@@ -4214,10 +4183,10 @@
     </row>
     <row r="57" customHeight="1" spans="2:4">
       <c r="B57" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D57" s="2">
         <v>323</v>
@@ -4225,10 +4194,10 @@
     </row>
     <row r="58" customHeight="1" spans="2:4">
       <c r="B58" s="15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D58" s="2">
         <v>324</v>
@@ -4236,10 +4205,10 @@
     </row>
     <row r="59" customHeight="1" spans="2:4">
       <c r="B59" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D59" s="2">
         <v>325</v>
@@ -4247,10 +4216,10 @@
     </row>
     <row r="60" customHeight="1" spans="2:4">
       <c r="B60" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D60" s="2">
         <v>326</v>
@@ -4258,10 +4227,10 @@
     </row>
     <row r="61" customHeight="1" spans="2:4">
       <c r="B61" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D61" s="2">
         <v>327</v>
@@ -4269,10 +4238,10 @@
     </row>
     <row r="62" customHeight="1" spans="2:4">
       <c r="B62" s="15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D62" s="2">
         <v>328</v>
@@ -4283,10 +4252,10 @@
     </row>
     <row r="64" customHeight="1" spans="2:4">
       <c r="B64" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D64" s="2">
         <v>416</v>
@@ -4294,10 +4263,10 @@
     </row>
     <row r="65" customHeight="1" spans="2:4">
       <c r="B65" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D65" s="2">
         <v>417</v>
@@ -4305,10 +4274,10 @@
     </row>
     <row r="66" customHeight="1" spans="2:4">
       <c r="B66" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2">
         <v>418</v>
@@ -4316,10 +4285,10 @@
     </row>
     <row r="67" customHeight="1" spans="2:4">
       <c r="B67" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D67" s="2">
         <v>419</v>
@@ -4327,10 +4296,10 @@
     </row>
     <row r="68" customHeight="1" spans="2:4">
       <c r="B68" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D68" s="2">
         <v>420</v>
@@ -4338,10 +4307,10 @@
     </row>
     <row r="69" customHeight="1" spans="2:4">
       <c r="B69" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D69" s="2">
         <v>421</v>
@@ -4349,10 +4318,10 @@
     </row>
     <row r="70" customHeight="1" spans="2:4">
       <c r="B70" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D70" s="2">
         <v>422</v>
@@ -4360,10 +4329,10 @@
     </row>
     <row r="71" customHeight="1" spans="2:4">
       <c r="B71" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D71" s="2">
         <v>423</v>
@@ -4371,10 +4340,10 @@
     </row>
     <row r="72" customHeight="1" spans="2:4">
       <c r="B72" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D72" s="2">
         <v>424</v>
@@ -4385,10 +4354,10 @@
     </row>
     <row r="74" customHeight="1" spans="2:4">
       <c r="B74" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D74" s="2">
         <v>2128</v>
@@ -4396,10 +4365,10 @@
     </row>
     <row r="75" customHeight="1" spans="2:4">
       <c r="B75" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D75" s="2">
         <v>2129</v>
@@ -4407,10 +4376,10 @@
     </row>
     <row r="76" customHeight="1" spans="2:4">
       <c r="B76" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D76" s="2">
         <v>2130</v>
@@ -4418,10 +4387,10 @@
     </row>
     <row r="77" customHeight="1" spans="2:4">
       <c r="B77" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D77" s="2">
         <v>2131</v>
@@ -4429,10 +4398,10 @@
     </row>
     <row r="78" customHeight="1" spans="2:4">
       <c r="B78" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D78" s="2">
         <v>2132</v>
@@ -4440,10 +4409,10 @@
     </row>
     <row r="79" customHeight="1" spans="2:4">
       <c r="B79" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D79" s="2">
         <v>2133</v>
@@ -4451,10 +4420,10 @@
     </row>
     <row r="80" customHeight="1" spans="2:4">
       <c r="B80" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D80" s="2">
         <v>2134</v>
@@ -4462,10 +4431,10 @@
     </row>
     <row r="81" customHeight="1" spans="2:4">
       <c r="B81" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D81" s="2">
         <v>2135</v>
@@ -4473,10 +4442,10 @@
     </row>
     <row r="82" customHeight="1" spans="2:4">
       <c r="B82" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D82" s="2">
         <v>2136</v>
@@ -4487,10 +4456,10 @@
     </row>
     <row r="84" customHeight="1" spans="2:4">
       <c r="B84" s="15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D84" s="2">
         <v>672</v>
@@ -4498,10 +4467,10 @@
     </row>
     <row r="85" customHeight="1" spans="2:4">
       <c r="B85" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D85" s="2">
         <v>673</v>
@@ -4509,10 +4478,10 @@
     </row>
     <row r="86" customHeight="1" spans="2:4">
       <c r="B86" s="15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D86" s="2">
         <v>674</v>
@@ -4520,10 +4489,10 @@
     </row>
     <row r="87" customHeight="1" spans="2:4">
       <c r="B87" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D87" s="2">
         <v>675</v>
@@ -4531,10 +4500,10 @@
     </row>
     <row r="88" customHeight="1" spans="2:4">
       <c r="B88" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D88" s="2">
         <v>676</v>
@@ -4542,10 +4511,10 @@
     </row>
     <row r="89" customHeight="1" spans="2:4">
       <c r="B89" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D89" s="2">
         <v>677</v>
@@ -4553,10 +4522,10 @@
     </row>
     <row r="90" customHeight="1" spans="2:4">
       <c r="B90" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D90" s="2">
         <v>678</v>
@@ -4564,10 +4533,10 @@
     </row>
     <row r="91" customHeight="1" spans="2:4">
       <c r="B91" s="15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D91" s="2">
         <v>679</v>
@@ -4575,10 +4544,10 @@
     </row>
     <row r="92" customHeight="1" spans="2:4">
       <c r="B92" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D92" s="2">
         <v>680</v>
@@ -4604,16 +4573,18 @@
     </row>
     <row r="99" customHeight="1" spans="1:4">
       <c r="A99" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B99" s="15"/>
+        <v>10</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="100" customHeight="1" spans="1:4">
       <c r="B100" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D100" s="2">
         <v>1440</v>
@@ -4621,10 +4592,10 @@
     </row>
     <row r="101" customHeight="1" spans="1:4">
       <c r="B101" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D101" s="2">
         <v>1520</v>
@@ -4632,10 +4603,10 @@
     </row>
     <row r="102" customHeight="1" spans="1:4">
       <c r="B102" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D102" s="2">
         <v>1600</v>
@@ -4646,10 +4617,10 @@
     </row>
     <row r="104" customHeight="1" spans="1:4">
       <c r="B104" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D104" s="2">
         <v>1441</v>
@@ -4657,10 +4628,10 @@
     </row>
     <row r="105" customHeight="1" spans="1:4">
       <c r="B105" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D105" s="2">
         <v>1521</v>
@@ -4668,10 +4639,10 @@
     </row>
     <row r="106" customHeight="1" spans="1:4">
       <c r="B106" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D106" s="2">
         <v>1601</v>
@@ -4682,10 +4653,10 @@
     </row>
     <row r="108" customHeight="1" spans="1:4">
       <c r="B108" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D108" s="2">
         <v>1448</v>
@@ -4693,10 +4664,10 @@
     </row>
     <row r="109" customHeight="1" spans="1:4">
       <c r="B109" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D109" s="2">
         <v>1528</v>
@@ -4704,10 +4675,10 @@
     </row>
     <row r="110" customHeight="1" spans="1:4">
       <c r="B110" s="15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D110" s="2">
         <v>1608</v>
@@ -4718,10 +4689,10 @@
     </row>
     <row r="112" customHeight="1" spans="1:4">
       <c r="B112" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D112" s="2">
         <v>1488</v>
@@ -4729,10 +4700,10 @@
     </row>
     <row r="113" customHeight="1" spans="1:4">
       <c r="B113" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D113" s="2">
         <v>1568</v>
@@ -4740,10 +4711,10 @@
     </row>
     <row r="114" customHeight="1" spans="1:4">
       <c r="B114" s="15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D114" s="2">
         <v>1648</v>
@@ -4754,10 +4725,10 @@
     </row>
     <row r="116" customHeight="1" spans="1:4">
       <c r="B116" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D116" s="2">
         <v>1489</v>
@@ -4765,10 +4736,10 @@
     </row>
     <row r="117" customHeight="1" spans="1:4">
       <c r="B117" s="15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D117" s="2">
         <v>1569</v>
@@ -4776,10 +4747,10 @@
     </row>
     <row r="118" customHeight="1" spans="1:4">
       <c r="B118" s="15" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D118" s="2">
         <v>1649</v>
@@ -4790,10 +4761,10 @@
     </row>
     <row r="120" customHeight="1" spans="1:4">
       <c r="B120" s="15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D120" s="2">
         <v>1490</v>
@@ -4801,10 +4772,10 @@
     </row>
     <row r="121" customHeight="1" spans="1:4">
       <c r="B121" s="15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D121" s="2">
         <v>1570</v>
@@ -4812,10 +4783,10 @@
     </row>
     <row r="122" customHeight="1" spans="1:4">
       <c r="B122" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D122" s="2">
         <v>1650</v>
@@ -4829,16 +4800,18 @@
     </row>
     <row r="125" customHeight="1" spans="1:4">
       <c r="A125" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B125" s="15"/>
+        <v>10</v>
+      </c>
+      <c r="B125" s="15" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="126" customHeight="1" spans="1:4">
       <c r="B126" s="15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D126" s="2">
         <v>1904</v>
@@ -4846,10 +4819,10 @@
     </row>
     <row r="127" customHeight="1" spans="1:4">
       <c r="B127" s="15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D127" s="2">
         <v>1905</v>
@@ -4857,10 +4830,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:4">
       <c r="B128" s="15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D128" s="2">
         <v>1906</v>
@@ -4868,10 +4841,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:4">
       <c r="B129" s="15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D129" s="2">
         <v>1907</v>
@@ -4879,10 +4852,10 @@
     </row>
     <row r="130" customHeight="1" spans="1:4">
       <c r="B130" s="15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D130" s="2">
         <v>1908</v>
@@ -4893,10 +4866,10 @@
     </row>
     <row r="132" customHeight="1" spans="1:4">
       <c r="B132" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D132" s="2">
         <v>1968</v>
@@ -4904,10 +4877,10 @@
     </row>
     <row r="133" customHeight="1" spans="1:4">
       <c r="B133" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D133" s="2">
         <v>1969</v>
@@ -4915,10 +4888,10 @@
     </row>
     <row r="134" customHeight="1" spans="1:4">
       <c r="B134" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D134" s="2">
         <v>1970</v>
@@ -4926,10 +4899,10 @@
     </row>
     <row r="135" customHeight="1" spans="1:4">
       <c r="B135" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D135" s="2">
         <v>1971</v>
@@ -4937,10 +4910,10 @@
     </row>
     <row r="136" customHeight="1" spans="1:4">
       <c r="B136" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D136" s="2">
         <v>1972</v>
@@ -4957,60 +4930,62 @@
     </row>
     <row r="140" customHeight="1" spans="1:4">
       <c r="A140" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B140" s="15"/>
+        <v>10</v>
+      </c>
+      <c r="B140" s="15" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="141" customHeight="1" spans="1:4">
       <c r="B141" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D141" s="2">
         <v>272</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="1:4">
-      <c r="B142" s="16" t="s">
-        <v>130</v>
+      <c r="B142" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D142" s="2">
         <v>273</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="1:4">
-      <c r="B143" s="16" t="s">
-        <v>131</v>
+      <c r="B143" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D143" s="2">
         <v>274</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="1:4">
-      <c r="B144" s="16" t="s">
-        <v>132</v>
+      <c r="B144" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D144" s="2">
         <v>275</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="2:4">
-      <c r="B145" s="16" t="s">
-        <v>133</v>
+      <c r="B145" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D145" s="2">
         <v>276</v>
